--- a/output/pdf_financials_xlsx/CGY.xlsx
+++ b/output/pdf_financials_xlsx/CGY.xlsx
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.715</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.753</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>40.724</v>
+        <v>40.009</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>32.243</v>
+        <v>31.49</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>13.181</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>41.97</v>
+        <v>41.255</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>33.187</v>
+        <v>32.434</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>13.181</v>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>18.47027241121331</v>
+        <v>18.15561325529199</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.38393788387994</v>
+        <v>15.03488237339205</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2866,34 +2866,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>43.662</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>29.055</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>30.742</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>31.998</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>29.782</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>10.624</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>16.761</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>28.639</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>21.842</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>51.788</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>46.101</v>
       </c>
     </row>
     <row r="35">
@@ -2994,34 +2994,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>43.662</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>29.055</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>30.742</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>31.998</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>29.782</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>10.624</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>16.761</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>28.639</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>21.842</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>51.788</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>46.101</v>
       </c>
     </row>
     <row r="37">
@@ -3762,34 +3762,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>51.469</v>
+        <v>7.807</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>36.495</v>
+        <v>7.44</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>33.944</v>
+        <v>3.202</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>33.712</v>
+        <v>1.714</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>31.313</v>
+        <v>1.531</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>27.091</v>
+        <v>1.891</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>12.497</v>
+        <v>1.873</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>18.339</v>
+        <v>1.578</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>30.412</v>
+        <v>1.773</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>26.742</v>
+        <v>4.9</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>44.447</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>94.15000000000001</v>
+        <v>48.049</v>
       </c>
     </row>
     <row r="49">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10819,7 +10819,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TotalNonCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -50170,7 +50170,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -51924,7 +51924,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -58152,7 +58152,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -65164,7 +65164,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E565" s="5" t="n">
